--- a/feedback_forms/037_developer_platform_feedback_inquiry_form--feedback_forms.xlsx
+++ b/feedback_forms/037_developer_platform_feedback_inquiry_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1014,8 +1014,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bug_reports'}</t>
+          <t>bug_reports</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bug reports'}</t>
+          <t>Bug reports</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'feature_suggestions'}</t>
+          <t>feature_suggestions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Feature suggestions'}</t>
+          <t>Feature suggestions</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'web'}</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Web'}</t>
+          <t>Web</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Very poor'}</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'extremely_poor'}</t>
+          <t>extremely_poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Extremely poor'}</t>
+          <t>Extremely poor</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available_and_responsive'}</t>
+          <t>available_and_responsive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available and responsive'}</t>
+          <t>Available and responsive</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'available,_but_slow'}</t>
+          <t>available,_but_slow</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Available, but slow'}</t>
+          <t>Available, but slow</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not available'}</t>
+          <t>Not available</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'unresponsive'}</t>
+          <t>unresponsive</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Unresponsive'}</t>
+          <t>Unresponsive</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available_and_responsive'}</t>
+          <t>available_and_responsive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available and responsive'}</t>
+          <t>Available and responsive</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'available,_but_slow'}</t>
+          <t>available,_but_slow</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Available, but slow'}</t>
+          <t>Available, but slow</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not available'}</t>
+          <t>Not available</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'unresponsive'}</t>
+          <t>unresponsive</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Unresponsive'}</t>
+          <t>Unresponsive</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available_and_responsive'}</t>
+          <t>available_and_responsive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available and responsive'}</t>
+          <t>Available and responsive</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'available,_but_slow'}</t>
+          <t>available,_but_slow</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Available, but slow'}</t>
+          <t>Available, but slow</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not available'}</t>
+          <t>Not available</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'unresponsive'}</t>
+          <t>unresponsive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Unresponsive'}</t>
+          <t>Unresponsive</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available_and_responsive'}</t>
+          <t>available_and_responsive</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available and responsive'}</t>
+          <t>Available and responsive</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'available,_but_slow'}</t>
+          <t>available,_but_slow</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Available, but slow'}</t>
+          <t>Available, but slow</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not available'}</t>
+          <t>Not available</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'unresponsive'}</t>
+          <t>unresponsive</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Unresponsive'}</t>
+          <t>Unresponsive</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available_and_responsive'}</t>
+          <t>available_and_responsive</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available and responsive'}</t>
+          <t>Available and responsive</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1587,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'available,_but_slow'}</t>
+          <t>available,_but_slow</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Available, but slow'}</t>
+          <t>Available, but slow</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not available'}</t>
+          <t>Not available</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'unresponsive'}</t>
+          <t>unresponsive</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Unresponsive'}</t>
+          <t>Unresponsive</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available_and_responsive'}</t>
+          <t>available_and_responsive</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available and responsive'}</t>
+          <t>Available and responsive</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'available,_but_slow'}</t>
+          <t>available,_but_slow</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Available, but slow'}</t>
+          <t>Available, but slow</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not available'}</t>
+          <t>Not available</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'unresponsive'}</t>
+          <t>unresponsive</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Unresponsive'}</t>
+          <t>Unresponsive</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available_and_responsive'}</t>
+          <t>available_and_responsive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available and responsive'}</t>
+          <t>Available and responsive</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'available,_but_slow'}</t>
+          <t>available,_but_slow</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Available, but slow'}</t>
+          <t>Available, but slow</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not available'}</t>
+          <t>Not available</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'unresponsive'}</t>
+          <t>unresponsive</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Unresponsive'}</t>
+          <t>Unresponsive</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'available_and_responsive'}</t>
+          <t>available_and_responsive</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Available and responsive'}</t>
+          <t>Available and responsive</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'available,_but_slow'}</t>
+          <t>available,_but_slow</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Available, but slow'}</t>
+          <t>Available, but slow</t>
         </is>
       </c>
     </row>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not available'}</t>
+          <t>Not available</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'unresponsive'}</t>
+          <t>unresponsive</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Unresponsive'}</t>
+          <t>Unresponsive</t>
         </is>
       </c>
     </row>
